--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,14 +729,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45163.6092721755</v>
+        <v>45163.60927217593</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -782,22 +778,6 @@
       </c>
       <c r="E11" s="11" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="18" customHeight="1" s="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -829,7 +809,7 @@
       </c>
       <c r="C29" s="27" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>113.01</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="1">
@@ -845,7 +825,7 @@
       </c>
       <c r="C30" s="27" t="n"/>
       <c r="D30" s="15" t="n">
-        <v>113.01</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="1">
@@ -861,7 +841,7 @@
       </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>113.01</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="1">
@@ -877,7 +857,7 @@
       </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="15" t="n">
-        <v>113.01</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="1">
@@ -893,7 +873,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>117.5</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="1">
@@ -909,7 +889,7 @@
       </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="15" t="n">
-        <v>117.5</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" s="1">
@@ -925,7 +905,7 @@
       </c>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="15" t="n">
-        <v>117.5</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="1">
@@ -941,7 +921,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="15" t="n">
-        <v>117.5</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="1">
@@ -976,7 +956,6 @@
         <v>124.4</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
@@ -984,7 +963,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
@@ -992,20 +970,12 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="1">
       <c r="A44" s="13" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="14" t="n"/>
     </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -1014,22 +984,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45163.60927217593</v>
+        <v>45219</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>112.95</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="1">
@@ -984,22 +984,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45219</v>
+        <v>45231</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
@@ -984,22 +984,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -987,8 +987,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B37:C37"/>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45231</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -984,22 +984,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
@@ -984,22 +984,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS/ma/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,10 +729,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45266</v>
+        <v>45230.54209495097</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -778,6 +782,22 @@
       </c>
       <c r="E11" s="11" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1" s="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -809,7 +829,7 @@
       </c>
       <c r="C29" s="27" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>108.7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="1">
@@ -825,7 +845,7 @@
       </c>
       <c r="C30" s="27" t="n"/>
       <c r="D30" s="15" t="n">
-        <v>108.7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="1">
@@ -841,7 +861,7 @@
       </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>108.7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="1">
@@ -857,7 +877,7 @@
       </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="15" t="n">
-        <v>108.7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="1">
@@ -873,7 +893,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>140</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="1">
@@ -889,7 +909,7 @@
       </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="15" t="n">
-        <v>112.95</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" s="1">
@@ -905,7 +925,7 @@
       </c>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="15" t="n">
-        <v>112.95</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="1">
@@ -921,7 +941,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="15" t="n">
-        <v>112.95</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="1">
@@ -937,7 +957,7 @@
       </c>
       <c r="C37" s="27" t="n"/>
       <c r="D37" s="15" t="n">
-        <v>124.4</v>
+        <v>143.06</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1" s="1">
@@ -953,9 +973,10 @@
       </c>
       <c r="C38" s="27" t="n"/>
       <c r="D38" s="15" t="n">
-        <v>124.4</v>
-      </c>
-    </row>
+        <v>143.06</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
@@ -963,6 +984,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
@@ -970,12 +992,20 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="1">
       <c r="A44" s="13" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="14" t="n"/>
     </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -984,22 +1014,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
